--- a/fuardan firma bulma/Robotsepeti_Tum_Fuar_Listesi_BirlestikOtomatik_Kurtarıldı.xlsx
+++ b/fuardan firma bulma/Robotsepeti_Tum_Fuar_Listesi_BirlestikOtomatik_Kurtarıldı.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6108114b979dbdba/Desktop/robotsepeti/İhracat/26.06.10- Hafta 8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GilboTeknik\Desktop\SKANOPT OÖC\fuardan firma bulma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{1E2FC3CF-9B7A-4BD2-B4F3-2428A87A349F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2F06A84-33BD-4D82-8BFF-DFB87EB1611C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B84BE06-F6AF-4807-89E3-882B35686D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1670" yWindow="6070" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Birleşik Tam Liste" sheetId="1" r:id="rId1"/>
@@ -1598,7 +1598,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1728,6 +1728,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1756,7 +1762,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1905,6 +1911,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2209,7 +2218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2227,7 +2236,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
@@ -2246,7 +2255,7 @@
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
@@ -2265,7 +2274,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2312,7 +2321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -2322,7 +2331,7 @@
       <c r="C4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="51" t="s">
         <v>43</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -2359,7 +2368,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -2369,7 +2378,7 @@
       <c r="C5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="51" t="s">
         <v>52</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -2400,7 +2409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2410,7 +2419,7 @@
       <c r="C6" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="51" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -2441,7 +2450,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2486,7 +2495,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -2531,7 +2540,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -2578,7 +2587,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -2623,7 +2632,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2668,7 +2677,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2713,7 +2722,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -2758,7 +2767,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -2803,7 +2812,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -2848,7 +2857,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -2893,7 +2902,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
@@ -2938,7 +2947,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
@@ -2983,7 +2992,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -3028,7 +3037,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -3073,7 +3082,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -3163,7 +3172,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -3210,7 +3219,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -3255,7 +3264,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
@@ -3300,7 +3309,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -3345,7 +3354,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -3390,7 +3399,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -3435,7 +3444,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -3480,7 +3489,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -3525,7 +3534,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
@@ -3570,7 +3579,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
@@ -3615,7 +3624,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -3660,7 +3669,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -3705,7 +3714,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>29</v>
       </c>
@@ -3750,7 +3759,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
@@ -3795,7 +3804,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>17</v>
       </c>
@@ -3836,7 +3845,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
@@ -3881,7 +3890,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>29</v>
       </c>
@@ -3922,7 +3931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>29</v>
       </c>
@@ -3969,7 +3978,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>17</v>
       </c>
@@ -4023,7 +4032,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4041,7 +4050,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>482</v>
       </c>
@@ -4060,7 +4069,7 @@
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -4107,7 +4116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -4154,7 +4163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -4201,7 +4210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -4246,7 +4255,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -4291,7 +4300,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -4336,7 +4345,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -4381,7 +4390,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -4426,7 +4435,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -4471,7 +4480,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -4516,7 +4525,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -4561,7 +4570,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -4606,7 +4615,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -4651,7 +4660,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -4696,7 +4705,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -4741,7 +4750,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
@@ -4786,7 +4795,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -4831,7 +4840,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
@@ -4876,7 +4885,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4921,7 +4930,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -4966,7 +4975,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -5011,7 +5020,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -5058,7 +5067,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -5103,7 +5112,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>17</v>
       </c>
@@ -5148,7 +5157,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
@@ -5193,7 +5202,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
@@ -5238,7 +5247,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -5283,7 +5292,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -5328,7 +5337,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
@@ -5373,7 +5382,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -5418,7 +5427,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
@@ -5463,7 +5472,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -5508,7 +5517,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
@@ -5553,7 +5562,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>29</v>
       </c>
@@ -5598,7 +5607,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
@@ -5643,7 +5652,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>29</v>
       </c>
@@ -5688,7 +5697,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
@@ -5733,7 +5742,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
@@ -5778,7 +5787,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -5823,7 +5832,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>17</v>
       </c>
@@ -5868,7 +5877,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>17</v>
       </c>
@@ -5915,7 +5924,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>17</v>
       </c>
@@ -5960,7 +5969,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>17</v>
       </c>
@@ -6005,7 +6014,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>17</v>
       </c>
@@ -6050,7 +6059,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>17</v>
       </c>
@@ -6095,7 +6104,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>17</v>
       </c>
@@ -6140,7 +6149,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>17</v>
       </c>
@@ -6185,7 +6194,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -6230,7 +6239,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
@@ -6275,7 +6284,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>29</v>
       </c>
@@ -6320,7 +6329,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>29</v>
       </c>
@@ -6365,7 +6374,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
@@ -6410,7 +6419,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
@@ -6455,7 +6464,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
@@ -6500,7 +6509,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
@@ -6545,7 +6554,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
@@ -6590,7 +6599,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>29</v>
       </c>
@@ -6635,7 +6644,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>29</v>
       </c>
@@ -6680,7 +6689,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>29</v>
       </c>
@@ -6725,7 +6734,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>17</v>
       </c>
@@ -6770,7 +6779,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>17</v>
       </c>
@@ -6815,7 +6824,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>17</v>
       </c>
@@ -6860,7 +6869,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>29</v>
       </c>
@@ -6905,7 +6914,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>29</v>
       </c>
@@ -6950,7 +6959,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>17</v>
       </c>
@@ -6997,7 +7006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -7044,7 +7053,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>29</v>
       </c>
@@ -7103,7 +7112,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -7121,7 +7130,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>483</v>
       </c>
@@ -7140,7 +7149,7 @@
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -7187,7 +7196,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -7234,7 +7243,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -7281,7 +7290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -7322,7 +7331,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -7363,7 +7372,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -7404,7 +7413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -7451,7 +7460,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -7492,7 +7501,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -7533,7 +7542,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -7574,7 +7583,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -7621,7 +7630,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -7668,7 +7677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -7709,7 +7718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -7756,7 +7765,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -7809,7 +7818,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -7827,7 +7836,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>484</v>
       </c>
@@ -7846,7 +7855,7 @@
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -7893,7 +7902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -7934,7 +7943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -7975,7 +7984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -8016,7 +8025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -8057,7 +8066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -8098,7 +8107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -8145,7 +8154,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -8186,7 +8195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -8227,7 +8236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -8280,7 +8289,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -8298,7 +8307,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>485</v>
       </c>
@@ -8317,7 +8326,7 @@
       <c r="N1" s="48"/>
       <c r="O1" s="48"/>
     </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
         <v>486</v>
       </c>
@@ -8336,7 +8345,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -8383,7 +8392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
@@ -8430,7 +8439,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -8477,7 +8486,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -8524,7 +8533,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -8571,7 +8580,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>17</v>
       </c>
@@ -8618,7 +8627,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -8665,7 +8674,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -8725,7 +8734,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -8733,7 +8742,7 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>487</v>
       </c>
@@ -8743,7 +8752,7 @@
       <c r="E1" s="48"/>
       <c r="F1" s="48"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>4</v>
       </c>
@@ -8763,7 +8772,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>64</v>
       </c>
@@ -8781,7 +8790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
         <v>86</v>
       </c>
@@ -8795,7 +8804,7 @@
       <c r="E4" s="27"/>
       <c r="F4" s="27"/>
     </row>
-    <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>226</v>
       </c>
@@ -8809,7 +8818,7 @@
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
     </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="s">
         <v>42</v>
       </c>
@@ -8829,7 +8838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>71</v>
       </c>
@@ -8845,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>78</v>
       </c>
@@ -8861,7 +8870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>403</v>
       </c>
@@ -8875,7 +8884,7 @@
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
     </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
         <v>19</v>
       </c>
@@ -8891,7 +8900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>51</v>
       </c>
@@ -8907,7 +8916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>285</v>
       </c>
@@ -8921,7 +8930,7 @@
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
     </row>
-    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>31</v>
       </c>
@@ -8939,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
         <v>171</v>
       </c>
@@ -8953,7 +8962,7 @@
       <c r="E14" s="27"/>
       <c r="F14" s="27"/>
     </row>
-    <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>181</v>
       </c>
@@ -8967,7 +8976,7 @@
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
     </row>
-    <row r="16" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="38" t="s">
         <v>189</v>
       </c>
@@ -8981,7 +8990,7 @@
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
     </row>
-    <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39" t="s">
         <v>199</v>
       </c>
@@ -8995,7 +9004,7 @@
       <c r="E17" s="27"/>
       <c r="F17" s="27"/>
     </row>
-    <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>399</v>
       </c>
@@ -9009,7 +9018,7 @@
       <c r="E18" s="27"/>
       <c r="F18" s="27"/>
     </row>
-    <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
         <v>417</v>
       </c>
@@ -9023,7 +9032,7 @@
       <c r="E19" s="27"/>
       <c r="F19" s="27"/>
     </row>
-    <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>436</v>
       </c>
@@ -9037,7 +9046,7 @@
       <c r="E20" s="27"/>
       <c r="F20" s="27"/>
     </row>
-    <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
         <v>475</v>
       </c>
@@ -9051,7 +9060,7 @@
       </c>
       <c r="F21" s="27"/>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
         <v>488</v>
       </c>
